--- a/test_samples/TRANS_DAYA_PRIMA/sample2_ref.xlsx
+++ b/test_samples/TRANS_DAYA_PRIMA/sample2_ref.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffrey.hu\Desktop\印尼供應商帳單\已丟測試\07. PT. TRANS DAYA PRIMA____________________OK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffrey.hu\Desktop\印尼sample\## 印尼 TOP 15 間 sample\10-TRANS DAYA PRIMA___VAT OK\$ 10-PT. TRANS DAYA PRIMA______OK VAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA1C462-558C-4613-9099-20F7B83B005C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762B75F1-99AB-4306-BDC5-CE8C3E81CE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9990" yWindow="2520" windowWidth="21660" windowHeight="14550" tabRatio="819" xr2:uid="{B2E6A21A-966E-4572-9141-AA1879003F42}"/>
+    <workbookView xWindow="9420" yWindow="6570" windowWidth="28800" windowHeight="12855" tabRatio="819" xr2:uid="{B2E6A21A-966E-4572-9141-AA1879003F42}"/>
   </bookViews>
   <sheets>
     <sheet name="DWIHARTA" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="41">
   <si>
     <t>INVOICE DATE
 發票日期</t>
@@ -200,6 +200,10 @@
   </si>
   <si>
     <t>Biaya Penumpukan</t>
+  </si>
+  <si>
+    <t>VAT (11%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -998,7 +1002,9 @@
       <c r="D7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="9"/>
+      <c r="E7" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9">
         <v>1148400</v>
@@ -1158,7 +1164,9 @@
       <c r="D10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6">
         <v>1012440</v>
